--- a/data/trans_dic/IP07_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>84,29%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>76,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87,97%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,01; 89,37</t>
+          <t>70,82; 83,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,03; 81,81</t>
+          <t>66,79; 78,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,16; 91,7</t>
+          <t>81,84; 91,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 88,59</t>
+          <t>73,27; 88,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,7; 83,66</t>
+          <t>78,19; 89,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,41; 78,93</t>
+          <t>69,97; 81,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,53; 92,21</t>
+          <t>82,17; 91,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,46; 90,2</t>
+          <t>70,89; 87,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,55; 85,16</t>
+          <t>76,33; 84,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70,36; 78,61</t>
+          <t>70,35; 78,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,0; 90,86</t>
+          <t>84,46; 90,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,2; 86,97</t>
+          <t>75,45; 86,2</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>76,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>78,42%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>87,22%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>77,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,87; 80,85</t>
+          <t>71,96; 80,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,06; 82,65</t>
+          <t>71,58; 80,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,15; 90,46</t>
+          <t>83,9; 90,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,67; 82,08</t>
+          <t>72,16; 82,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,93; 80,62</t>
+          <t>71,96; 80,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,85; 80,52</t>
+          <t>74,1; 82,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,98; 90,86</t>
+          <t>82,22; 90,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,92; 82,6</t>
+          <t>70,25; 81,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,57; 79,9</t>
+          <t>73,46; 79,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,94; 80,28</t>
+          <t>74,17; 80,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,7; 89,68</t>
+          <t>84,65; 89,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,18; 81,0</t>
+          <t>72,94; 80,87</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,87%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82,01%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74,26%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>71,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>88,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,98%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,01%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69,59; 81,87</t>
+          <t>67,6; 79,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,37; 77,68</t>
+          <t>68,37; 79,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,54; 92,17</t>
+          <t>76,79; 86,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,73; 79,42</t>
+          <t>68,82; 80,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,46; 79,41</t>
+          <t>69,72; 81,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,2; 79,62</t>
+          <t>65,63; 77,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,38; 85,95</t>
+          <t>84,53; 92,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,31; 79,74</t>
+          <t>67,85; 79,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,0; 79,13</t>
+          <t>70,9; 78,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,54; 76,9</t>
+          <t>68,47; 76,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82,13; 88,27</t>
+          <t>82,39; 88,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,68; 77,96</t>
+          <t>69,75; 77,85</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>74,66%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>76,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>73,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>84,63%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,0; 80,59</t>
+          <t>73,01; 82,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,46; 78,31</t>
+          <t>69,1; 79,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 88,69</t>
+          <t>81,07; 90,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,03; 84,05</t>
+          <t>66,58; 79,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,42; 82,48</t>
+          <t>70,81; 80,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,27; 79,48</t>
+          <t>67,56; 78,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,67; 90,22</t>
+          <t>79,95; 88,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,89; 80,22</t>
+          <t>72,7; 81,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,71; 80,53</t>
+          <t>73,66; 80,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,3; 77,78</t>
+          <t>69,92; 77,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,89; 88,54</t>
+          <t>82,2; 88,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,89; 80,96</t>
+          <t>71,19; 79,54</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 80,03</t>
+          <t>73,77; 79,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,53; 77,8</t>
+          <t>71,91; 77,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,71; 89,13</t>
+          <t>83,79; 88,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,84</t>
+          <t>71,89; 78,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,05; 79,23</t>
+          <t>74,85; 79,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,88; 77,31</t>
+          <t>72,36; 78,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,01</t>
+          <t>85,05; 89,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 78,85</t>
+          <t>73,47; 79,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75,32; 78,93</t>
+          <t>75,46; 79,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,06; 76,72</t>
+          <t>73,08; 76,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85,09; 87,93</t>
+          <t>85,07; 87,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 78,72</t>
+          <t>73,47; 78,1</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94428</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106179</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>108373</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>89487</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>112021</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>115180</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46939</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94428</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>106179</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>108373</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>42157</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>83457</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82819; 94880</t>
+          <t>85958; 101330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102775; 120070</t>
+          <t>97031; 114672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108883; 120068</t>
+          <t>100989; 113435</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42314; 50949</t>
+          <t>37026; 44854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>87034; 101546</t>
+          <t>83018; 94931</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96484; 114662</t>
+          <t>102684; 119634</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100601; 113777</t>
+          <t>107588; 119941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45752; 55422</t>
+          <t>36928; 45596</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174194; 193787</t>
+          <t>173684; 192914</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205478; 229558</t>
+          <t>205450; 229921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>213633; 231068</t>
+          <t>214812; 231229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90646; 103459</t>
+          <t>77436; 88461</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>286</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>193</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>193010</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202707</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>225359</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>193785</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>184106</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>181493</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123028</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>193010</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>202707</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>225359</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>141586</t>
+          <t>110606</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>264614</t>
+          <t>232916</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>181983; 204718</t>
+          <t>181533; 203399</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173860; 194033</t>
+          <t>190430; 214145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173022; 188242</t>
+          <t>215981; 233586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114167; 130745</t>
+          <t>113667; 130504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>181455; 203363</t>
+          <t>182202; 203740</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>191163; 214212</t>
+          <t>173960; 194603</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>216182; 233880</t>
+          <t>171077; 187580</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>131300; 150788</t>
+          <t>102224; 118076</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>371856; 403880</t>
+          <t>371326; 402177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>370310; 402069</t>
+          <t>371474; 401640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>394296; 417476</t>
+          <t>394056; 417189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>250172; 276889</t>
+          <t>221051; 245067</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>169</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104513</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117137</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154649</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>97448</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>112621</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>167440</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128644</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>104513</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>117137</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>154649</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157611</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>286255</t>
+          <t>277573</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88755; 104425</t>
+          <t>95662; 112850</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102661; 121998</t>
+          <t>108415; 126543</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159132; 173480</t>
+          <t>144799; 163046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117774; 138101</t>
+          <t>137720; 160110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95461; 112376</t>
+          <t>88923; 104100</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>108142; 126252</t>
+          <t>103069; 121438</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>144025; 162078</t>
+          <t>159097; 173413</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>143023; 169433</t>
+          <t>119086; 139139</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191040; 212919</t>
+          <t>190771; 212204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216314; 242719</t>
+          <t>216090; 242280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>309466; 332612</t>
+          <t>310457; 332633</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>269220; 301231</t>
+          <t>262006; 292457</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>261</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>160073</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134292</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149055</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>218488</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>147750</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>124890</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>146014</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>216235</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>160073</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>134292</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>149055</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>229686</t>
+          <t>199531</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>445920</t>
+          <t>418019</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>137800; 156427</t>
+          <t>149480; 168991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>113385; 133596</t>
+          <t>124347; 143351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137303; 153015</t>
+          <t>139968; 155761</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>198406; 231527</t>
+          <t>194838; 233085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>150314; 168865</t>
+          <t>137442; 156831</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124650; 143034</t>
+          <t>115253; 134635</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140989; 155765</t>
+          <t>137941; 153286</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>201272; 245058</t>
+          <t>186523; 209741</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>293964; 321173</t>
+          <t>293797; 320624</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246442; 272676</t>
+          <t>245116; 271752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>282668; 305636</t>
+          <t>283740; 306183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>417639; 470324</t>
+          <t>390961; 436842</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>712</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>552024</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>560316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>514845</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>552024</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>560316</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>481245</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1094524</t>
+          <t>1011965</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>510969; 544993</t>
+          <t>531032; 569418</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>514352; 551741</t>
+          <t>539212; 577892</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>592800; 623724</t>
+          <t>621765; 653037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>493501; 538549</t>
+          <t>503826; 550622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>533092; 570402</t>
+          <t>509734; 544114</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>538961; 579701</t>
+          <t>513145; 553843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>620838; 653042</t>
+          <t>595178; 622956</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>546755; 600807</t>
+          <t>462596; 497545</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1055193; 1105701</t>
+          <t>1057138; 1107039</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1065909; 1119379</t>
+          <t>1066253; 1120739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1226851; 1267830</t>
+          <t>1226504; 1268462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1056234; 1124260</t>
+          <t>977554; 1039155</t>
         </is>
       </c>
     </row>
